--- a/model/data/invoice/sale/1405-04-21-sale-zibavash-express.xlsx
+++ b/model/data/invoice/sale/1405-04-21-sale-zibavash-express.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,47 +421,67 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v xml:space="preserve">رژ لب مایع گلدن رز شماره 43 </v>
+        <v xml:space="preserve">ژل ابرو کولمار مدل آرگان دار </v>
       </c>
       <c r="B2">
-        <v>38091065</v>
+        <v>63117035</v>
       </c>
       <c r="C2">
-        <v>10618527</v>
+        <v>15831542</v>
       </c>
       <c r="D2">
-        <v>7794700</v>
+        <v>4180000</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>00221403</v>
+        <v>00230049</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">کرم پودر گلدن رز مدل Matte Perfection شماره W4 حجم 35 میلی لیتر </v>
+        <v xml:space="preserve">خط چشم گلدن رز مدل EYELINER </v>
       </c>
       <c r="B3">
-        <v>45754984</v>
+        <v>33859103</v>
       </c>
       <c r="C3">
-        <v>13235102</v>
+        <v>1051842</v>
       </c>
       <c r="D3">
-        <v>8435200</v>
+        <v>3453100</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>00221567</v>
+        <v>00221245</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v xml:space="preserve">مداد لب گلدن رز مدل DREAM شماره 519 </v>
+      </c>
+      <c r="B4">
+        <v>37200241</v>
+      </c>
+      <c r="C4">
+        <v>1051594</v>
+      </c>
+      <c r="D4">
+        <v>2457700</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>00221229</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>